--- a/thaco/color/1_MID_Office_TEMP.xlsx
+++ b/thaco/color/1_MID_Office_TEMP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C328DA69-8021-0B4F-90A9-27EEB24165D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C0F26C-DA03-B94F-A168-129A94B4D888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="74360" yWindow="4420" windowWidth="38280" windowHeight="18260" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38520" yWindow="500" windowWidth="38280" windowHeight="14380" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
